--- a/public/templates/importamaazonxlsx.xlsx
+++ b/public/templates/importamaazonxlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5ac39e7ed8509f1b/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{6E2BF883-7D8D-4721-A857-3D0C490DA340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD5EE629-DF3B-449C-A8FA-97919FFE6E94}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{6E2BF883-7D8D-4721-A857-3D0C490DA340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D60F5B1E-DFD7-4E92-A780-1877ADDBF1F7}"/>
   <bookViews>
-    <workbookView xWindow="12" yWindow="12" windowWidth="23016" windowHeight="12216" xr2:uid="{3B07CEA4-1129-4E7F-B194-49CA58545786}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3B07CEA4-1129-4E7F-B194-49CA58545786}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Link Product</t>
   </si>
@@ -48,6 +48,9 @@
   </si>
   <si>
     <t>Keyword Phrase</t>
+  </si>
+  <si>
+    <t>Product</t>
   </si>
 </sst>
 </file>
@@ -76,15 +79,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -92,15 +101,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -117,6 +144,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -436,10 +467,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5213E118-EEFE-4B8B-8BFC-C62A12C3B2A0}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="3" max="3" width="34.21875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4" ht="15" thickBot="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -447,13 +481,16 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="2"/>
+    <row r="2" spans="1:4" ht="15" thickBot="1">
+      <c r="A2" s="3"/>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:4">
       <c r="A3" s="2"/>
     </row>
   </sheetData>

--- a/public/templates/importamaazonxlsx.xlsx
+++ b/public/templates/importamaazonxlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5ac39e7ed8509f1b/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{6E2BF883-7D8D-4721-A857-3D0C490DA340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D60F5B1E-DFD7-4E92-A780-1877ADDBF1F7}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{6E2BF883-7D8D-4721-A857-3D0C490DA340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26B7B7FD-9638-4C09-93F8-2F377D7A32F1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3B07CEA4-1129-4E7F-B194-49CA58545786}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Link Product</t>
   </si>
@@ -51,6 +51,9 @@
   </si>
   <si>
     <t>Product</t>
+  </si>
+  <si>
+    <t>SKU</t>
   </si>
 </sst>
 </file>
@@ -467,31 +470,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5213E118-EEFE-4B8B-8BFC-C62A12C3B2A0}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="3" max="3" width="34.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" thickBot="1">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" ht="15" thickBot="1">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" thickBot="1">
-      <c r="A2" s="3"/>
+    <row r="2" spans="1:5" ht="15" thickBot="1">
+      <c r="B2" s="3"/>
     </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="2"/>
+    <row r="3" spans="1:5">
+      <c r="B3" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
